--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/78.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/78.xlsx
@@ -426,13 +426,13 @@
         <v>-12.35432053867263</v>
       </c>
       <c r="E2">
-        <v>-9.31693431330268</v>
+        <v>-9.685393600936779</v>
       </c>
       <c r="F2">
-        <v>0.8269036838638579</v>
+        <v>0.4659430560580259</v>
       </c>
       <c r="G2">
-        <v>-10.68218478987222</v>
+        <v>-10.8342083515811</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.18438571432124</v>
       </c>
       <c r="E3">
-        <v>-9.417036231242234</v>
+        <v>-8.729029703730884</v>
       </c>
       <c r="F3">
-        <v>0.6878812274888368</v>
+        <v>0.8783266149381768</v>
       </c>
       <c r="G3">
-        <v>-10.28016869231083</v>
+        <v>-9.954603022887818</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.803304594071925</v>
       </c>
       <c r="E4">
-        <v>-10.0104157658893</v>
+        <v>-9.961431262548333</v>
       </c>
       <c r="F4">
-        <v>1.068174945257396</v>
+        <v>0.937048846576756</v>
       </c>
       <c r="G4">
-        <v>-9.415973953102858</v>
+        <v>-9.34010618097938</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.346274255097743</v>
       </c>
       <c r="E5">
-        <v>-11.37093691133176</v>
+        <v>-11.11452112759544</v>
       </c>
       <c r="F5">
-        <v>1.036302863709177</v>
+        <v>1.414509257081187</v>
       </c>
       <c r="G5">
-        <v>-9.411388847530967</v>
+        <v>-8.957691823556008</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-6.832420552770025</v>
       </c>
       <c r="E6">
-        <v>-12.44448865890815</v>
+        <v>-11.11161384728252</v>
       </c>
       <c r="F6">
-        <v>0.9327617546636614</v>
+        <v>0.8318305929667901</v>
       </c>
       <c r="G6">
-        <v>-8.370804931445091</v>
+        <v>-8.686018524966796</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-5.315375260364098</v>
       </c>
       <c r="E7">
-        <v>-12.90020258372204</v>
+        <v>-12.05523914710484</v>
       </c>
       <c r="F7">
-        <v>1.191352423948445</v>
+        <v>0.4130536133060101</v>
       </c>
       <c r="G7">
-        <v>-8.717743482869633</v>
+        <v>-7.354348271249423</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-3.821583880617932</v>
       </c>
       <c r="E8">
-        <v>-13.4540757111262</v>
+        <v>-13.48368740266235</v>
       </c>
       <c r="F8">
-        <v>1.353188164035372</v>
+        <v>0.7739635625225481</v>
       </c>
       <c r="G8">
-        <v>-8.606376730928551</v>
+        <v>-6.441207116243329</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-2.393766759837376</v>
       </c>
       <c r="E9">
-        <v>-14.35771911393479</v>
+        <v>-13.85142666292923</v>
       </c>
       <c r="F9">
-        <v>1.525481114281944</v>
+        <v>1.077488719746095</v>
       </c>
       <c r="G9">
-        <v>-7.124857943921604</v>
+        <v>-6.658352419255205</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-1.040611861226795</v>
       </c>
       <c r="E10">
-        <v>-13.81043038773779</v>
+        <v>-14.2741823539153</v>
       </c>
       <c r="F10">
-        <v>1.694164798747231</v>
+        <v>1.382188986758899</v>
       </c>
       <c r="G10">
-        <v>-5.670872964164777</v>
+        <v>-5.545340387861153</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>0.2187670610368979</v>
       </c>
       <c r="E11">
-        <v>-15.901109096755</v>
+        <v>-15.79225816703262</v>
       </c>
       <c r="F11">
-        <v>1.673890195617775</v>
+        <v>1.136635384570012</v>
       </c>
       <c r="G11">
-        <v>-5.214302386661731</v>
+        <v>-4.249708732884286</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>1.376057423941969</v>
       </c>
       <c r="E12">
-        <v>-16.37656716824233</v>
+        <v>-17.03723076969537</v>
       </c>
       <c r="F12">
-        <v>1.909705590132624</v>
+        <v>1.681311441537524</v>
       </c>
       <c r="G12">
-        <v>-5.240223958234225</v>
+        <v>-4.384663121792675</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>2.442375386431681</v>
       </c>
       <c r="E13">
-        <v>-17.12906822257092</v>
+        <v>-16.48110246223539</v>
       </c>
       <c r="F13">
-        <v>2.354009533591415</v>
+        <v>1.262530502611956</v>
       </c>
       <c r="G13">
-        <v>-4.302435791688258</v>
+        <v>-4.337133619485359</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>3.413132458168812</v>
       </c>
       <c r="E14">
-        <v>-18.61877314603019</v>
+        <v>-18.05453887009649</v>
       </c>
       <c r="F14">
-        <v>2.080048998397291</v>
+        <v>1.753895851053945</v>
       </c>
       <c r="G14">
-        <v>-4.06172271498231</v>
+        <v>-3.166478369161517</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>4.292446031271205</v>
       </c>
       <c r="E15">
-        <v>-18.69203027005227</v>
+        <v>-19.06909365830095</v>
       </c>
       <c r="F15">
-        <v>2.93098685641023</v>
+        <v>1.913354448561797</v>
       </c>
       <c r="G15">
-        <v>-3.384126875095363</v>
+        <v>-2.955205973936309</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>5.091916765248527</v>
       </c>
       <c r="E16">
-        <v>-19.29989639304988</v>
+        <v>-19.61911305432458</v>
       </c>
       <c r="F16">
-        <v>3.143409330848123</v>
+        <v>2.389069615147414</v>
       </c>
       <c r="G16">
-        <v>-3.089332726459881</v>
+        <v>-2.13089668738548</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>5.810334711547559</v>
       </c>
       <c r="E17">
-        <v>-22.02158172724389</v>
+        <v>-20.68976657853606</v>
       </c>
       <c r="F17">
-        <v>2.998033046340359</v>
+        <v>2.542044520637456</v>
       </c>
       <c r="G17">
-        <v>-2.937862025856067</v>
+        <v>-0.9231004266565547</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>6.449943272409194</v>
       </c>
       <c r="E18">
-        <v>-22.34962891283354</v>
+        <v>-21.83937404707127</v>
       </c>
       <c r="F18">
-        <v>3.006315828278107</v>
+        <v>2.533254952806767</v>
       </c>
       <c r="G18">
-        <v>-2.411601154205823</v>
+        <v>-1.707729514373679</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>7.012150501467358</v>
       </c>
       <c r="E19">
-        <v>-22.74974223378126</v>
+        <v>-22.02734194618165</v>
       </c>
       <c r="F19">
-        <v>3.168772381083885</v>
+        <v>2.792287476041959</v>
       </c>
       <c r="G19">
-        <v>-2.87588861336091</v>
+        <v>-2.392691318085506</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>7.488215318442177</v>
       </c>
       <c r="E20">
-        <v>-23.24626676635227</v>
+        <v>-23.55887638404977</v>
       </c>
       <c r="F20">
-        <v>3.430677746849685</v>
+        <v>3.075368573603098</v>
       </c>
       <c r="G20">
-        <v>-1.622327371097101</v>
+        <v>-0.5381965389876507</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>7.871945885211674</v>
       </c>
       <c r="E21">
-        <v>-24.31694293293379</v>
+        <v>-22.81372051456162</v>
       </c>
       <c r="F21">
-        <v>3.64101923171469</v>
+        <v>3.733328698407909</v>
       </c>
       <c r="G21">
-        <v>-1.323838653639793</v>
+        <v>-0.8124752369162687</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>8.156608465466054</v>
       </c>
       <c r="E22">
-        <v>-24.43314357597061</v>
+        <v>-24.34074006384409</v>
       </c>
       <c r="F22">
-        <v>3.750245844996633</v>
+        <v>3.160728738739369</v>
       </c>
       <c r="G22">
-        <v>-1.811981903950868</v>
+        <v>-0.4006235085576973</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>8.329509090998345</v>
       </c>
       <c r="E23">
-        <v>-25.98519652956749</v>
+        <v>-25.64700556220066</v>
       </c>
       <c r="F23">
-        <v>3.595546283764677</v>
+        <v>3.462109558153411</v>
       </c>
       <c r="G23">
-        <v>-1.257127850477939</v>
+        <v>-0.9749832963480126</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>8.387830711717751</v>
       </c>
       <c r="E24">
-        <v>-25.31552579331319</v>
+        <v>-25.48180683040084</v>
       </c>
       <c r="F24">
-        <v>3.854893964477041</v>
+        <v>3.309722207557996</v>
       </c>
       <c r="G24">
-        <v>-1.569805566116563</v>
+        <v>-0.3144897347169396</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>8.333152988629054</v>
       </c>
       <c r="E25">
-        <v>-24.99003719553788</v>
+        <v>-24.79904427579037</v>
       </c>
       <c r="F25">
-        <v>3.657332986349632</v>
+        <v>3.320706791787484</v>
       </c>
       <c r="G25">
-        <v>-0.638668285558992</v>
+        <v>-0.6489673927316647</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>8.166223021916284</v>
       </c>
       <c r="E26">
-        <v>-24.89055567853738</v>
+        <v>-26.77161132573952</v>
       </c>
       <c r="F26">
-        <v>3.713893459413636</v>
+        <v>3.152531476921054</v>
       </c>
       <c r="G26">
-        <v>-0.9862954304557023</v>
+        <v>0.08895982906296142</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>7.899535380577959</v>
       </c>
       <c r="E27">
-        <v>-25.06271014641297</v>
+        <v>-25.25892892516533</v>
       </c>
       <c r="F27">
-        <v>3.651986395179108</v>
+        <v>3.75558768504941</v>
       </c>
       <c r="G27">
-        <v>-0.9353527556973973</v>
+        <v>0.6937534619957968</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>7.548306926718705</v>
       </c>
       <c r="E28">
-        <v>-25.43108339304093</v>
+        <v>-25.39014598801159</v>
       </c>
       <c r="F28">
-        <v>3.666882733019732</v>
+        <v>2.75962354153602</v>
       </c>
       <c r="G28">
-        <v>-0.1397293462443529</v>
+        <v>-0.2645633974391908</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>7.124737602723909</v>
       </c>
       <c r="E29">
-        <v>-24.68147603360324</v>
+        <v>-24.40867170243316</v>
       </c>
       <c r="F29">
-        <v>3.233701156205072</v>
+        <v>3.46682583436959</v>
       </c>
       <c r="G29">
-        <v>-0.6183382254023276</v>
+        <v>1.415799996838539</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>6.651117916712527</v>
       </c>
       <c r="E30">
-        <v>-24.4333156579829</v>
+        <v>-24.64026239165943</v>
       </c>
       <c r="F30">
-        <v>3.340645649262867</v>
+        <v>3.040492201933291</v>
       </c>
       <c r="G30">
-        <v>-0.458654061315582</v>
+        <v>-0.1014197132639067</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>6.145192180989618</v>
       </c>
       <c r="E31">
-        <v>-24.15333369551066</v>
+        <v>-25.0381658172914</v>
       </c>
       <c r="F31">
-        <v>3.342554014890972</v>
+        <v>3.162755882311131</v>
       </c>
       <c r="G31">
-        <v>-0.1920061708549842</v>
+        <v>-0.1078818981565641</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>5.619503928049749</v>
       </c>
       <c r="E32">
-        <v>-24.26172272088425</v>
+        <v>-24.30017399368338</v>
       </c>
       <c r="F32">
-        <v>3.314945269667116</v>
+        <v>3.189316214218966</v>
       </c>
       <c r="G32">
-        <v>-0.9498926717058763</v>
+        <v>-0.1837331175523455</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>5.095770717367703</v>
       </c>
       <c r="E33">
-        <v>-23.64619894833968</v>
+        <v>-23.77718958748555</v>
       </c>
       <c r="F33">
-        <v>3.153576722825244</v>
+        <v>2.957846508736083</v>
       </c>
       <c r="G33">
-        <v>-1.137206648863379</v>
+        <v>0.5554686642749</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>4.583403896759284</v>
       </c>
       <c r="E34">
-        <v>-23.33924086620375</v>
+        <v>-23.7550770489061</v>
       </c>
       <c r="F34">
-        <v>3.27106394616212</v>
+        <v>2.715670951264829</v>
       </c>
       <c r="G34">
-        <v>-1.499827254507449</v>
+        <v>-0.3975413906606359</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>4.089640740593373</v>
       </c>
       <c r="E35">
-        <v>-22.83811087556693</v>
+        <v>-23.25581731803445</v>
       </c>
       <c r="F35">
-        <v>3.267757168210682</v>
+        <v>2.633520958019154</v>
       </c>
       <c r="G35">
-        <v>-0.9782441837041947</v>
+        <v>-0.1205977035729047</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>3.62585314879275</v>
       </c>
       <c r="E36">
-        <v>-22.79531226772044</v>
+        <v>-23.37287837113272</v>
       </c>
       <c r="F36">
-        <v>2.905316567226872</v>
+        <v>2.890759142452152</v>
       </c>
       <c r="G36">
-        <v>-1.024624926709384</v>
+        <v>-0.02482693166732855</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>3.18997248817292</v>
       </c>
       <c r="E37">
-        <v>-21.14352873105264</v>
+        <v>-22.4860446638406</v>
       </c>
       <c r="F37">
-        <v>3.277680669476826</v>
+        <v>2.968297384072068</v>
       </c>
       <c r="G37">
-        <v>-1.39839213918418</v>
+        <v>-0.7357334807704232</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>2.781909323632471</v>
       </c>
       <c r="E38">
-        <v>-19.88370726211874</v>
+        <v>-22.28358564790567</v>
       </c>
       <c r="F38">
-        <v>3.306833527968235</v>
+        <v>2.744066798328658</v>
       </c>
       <c r="G38">
-        <v>-1.873091264060275</v>
+        <v>-1.044170387573241</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>2.399859320143005</v>
       </c>
       <c r="E39">
-        <v>-19.98393597733051</v>
+        <v>-20.46406290551976</v>
       </c>
       <c r="F39">
-        <v>3.182143610127941</v>
+        <v>2.912555686966345</v>
       </c>
       <c r="G39">
-        <v>-1.850824534763137</v>
+        <v>-0.07954031779486345</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>2.032645675295957</v>
       </c>
       <c r="E40">
-        <v>-19.12044202507392</v>
+        <v>-19.63926476365871</v>
       </c>
       <c r="F40">
-        <v>3.289605975020085</v>
+        <v>2.86842413792671</v>
       </c>
       <c r="G40">
-        <v>-2.202566687765162</v>
+        <v>-0.2174708871430582</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>1.673996630684132</v>
       </c>
       <c r="E41">
-        <v>-18.83626216719658</v>
+        <v>-18.93450741079299</v>
       </c>
       <c r="F41">
-        <v>3.334603811195465</v>
+        <v>2.859110363438011</v>
       </c>
       <c r="G41">
-        <v>-2.259047905210667</v>
+        <v>-1.045246314873504</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>1.316212509736091</v>
       </c>
       <c r="E42">
-        <v>-18.49023693979648</v>
+        <v>-17.76649169541659</v>
       </c>
       <c r="F42">
-        <v>3.42550853074169</v>
+        <v>3.02638296593264</v>
       </c>
       <c r="G42">
-        <v>-1.758430519307618</v>
+        <v>-0.833159525445635</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.9462001226973288</v>
       </c>
       <c r="E43">
-        <v>-18.28000706246439</v>
+        <v>-18.05889526209187</v>
       </c>
       <c r="F43">
-        <v>3.493036167270112</v>
+        <v>2.589517689158669</v>
       </c>
       <c r="G43">
-        <v>-2.532240744202404</v>
+        <v>-1.334975328833901</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>0.5612494573655404</v>
       </c>
       <c r="E44">
-        <v>-17.09203436213619</v>
+        <v>-18.05876846481965</v>
       </c>
       <c r="F44">
-        <v>3.325367638296623</v>
+        <v>3.143371321906153</v>
       </c>
       <c r="G44">
-        <v>-2.385735861907497</v>
+        <v>-0.9597382341396689</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>0.1580240021465041</v>
       </c>
       <c r="E45">
-        <v>-15.69597828115554</v>
+        <v>-16.33979143082604</v>
       </c>
       <c r="F45">
-        <v>3.329041836020442</v>
+        <v>2.896962518522929</v>
       </c>
       <c r="G45">
-        <v>-3.3576094053258</v>
+        <v>-1.744979772781559</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.2697457648511256</v>
       </c>
       <c r="E46">
-        <v>-15.545696342737</v>
+        <v>-15.51761527541543</v>
       </c>
       <c r="F46">
-        <v>3.117618680015191</v>
+        <v>2.754048896713673</v>
       </c>
       <c r="G46">
-        <v>-2.862974175212214</v>
+        <v>-2.765157486163368</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.7195468908763094</v>
       </c>
       <c r="E47">
-        <v>-15.22516189552607</v>
+        <v>-15.60895912462415</v>
       </c>
       <c r="F47">
-        <v>3.67837410314216</v>
+        <v>2.261441922833979</v>
       </c>
       <c r="G47">
-        <v>-3.006843863257861</v>
+        <v>-2.193512345715255</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.189339702198898</v>
       </c>
       <c r="E48">
-        <v>-13.47417307877224</v>
+        <v>-14.31310005953722</v>
       </c>
       <c r="F48">
-        <v>3.979040671188339</v>
+        <v>2.832264964465396</v>
       </c>
       <c r="G48">
-        <v>-4.179713868547474</v>
+        <v>-2.919687130845468</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.678965004552558</v>
       </c>
       <c r="E49">
-        <v>-13.24134611614187</v>
+        <v>-14.38357217204458</v>
       </c>
       <c r="F49">
-        <v>3.48115045437474</v>
+        <v>2.925529405825626</v>
       </c>
       <c r="G49">
-        <v>-3.282453400493266</v>
+        <v>-2.834897438493654</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.181541364529287</v>
       </c>
       <c r="E50">
-        <v>-12.86493482815031</v>
+        <v>-12.57227313845659</v>
       </c>
       <c r="F50">
-        <v>3.391884870450995</v>
+        <v>3.1051976745204</v>
       </c>
       <c r="G50">
-        <v>-4.073167270911571</v>
+        <v>-2.41002533452913</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.69535196474952</v>
       </c>
       <c r="E51">
-        <v>-12.43959337850586</v>
+        <v>-13.33208767830757</v>
       </c>
       <c r="F51">
-        <v>3.442599884981112</v>
+        <v>3.369679729810619</v>
       </c>
       <c r="G51">
-        <v>-4.229716348372627</v>
+        <v>-3.08475093143353</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.219248107841715</v>
       </c>
       <c r="E52">
-        <v>-11.48220604617423</v>
+        <v>-12.2300291868529</v>
       </c>
       <c r="F52">
-        <v>3.809541378176601</v>
+        <v>3.463805707188847</v>
       </c>
       <c r="G52">
-        <v>-4.143188619612696</v>
+        <v>-2.849119542130364</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.744061448926384</v>
       </c>
       <c r="E53">
-        <v>-12.40770386454384</v>
+        <v>-11.58439106215731</v>
       </c>
       <c r="F53">
-        <v>3.383690776044511</v>
+        <v>3.116587687464241</v>
       </c>
       <c r="G53">
-        <v>-4.257667284360694</v>
+        <v>-2.85835596418493</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.271021663070003</v>
       </c>
       <c r="E54">
-        <v>-9.998157186750539</v>
+        <v>-10.23655870088434</v>
       </c>
       <c r="F54">
-        <v>3.255453356953633</v>
+        <v>3.622971319102342</v>
       </c>
       <c r="G54">
-        <v>-4.536362250038699</v>
+        <v>-4.079960510358156</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.796328539519628</v>
       </c>
       <c r="E55">
-        <v>-10.02303662294868</v>
+        <v>-9.882169381992078</v>
       </c>
       <c r="F55">
-        <v>3.480895477722354</v>
+        <v>2.89377768592698</v>
       </c>
       <c r="G55">
-        <v>-5.306573911932298</v>
+        <v>-4.443789465124059</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.309949190652459</v>
       </c>
       <c r="E56">
-        <v>-9.771257996596216</v>
+        <v>-9.483989719445638</v>
       </c>
       <c r="F56">
-        <v>3.504815771869151</v>
+        <v>3.319328967641052</v>
       </c>
       <c r="G56">
-        <v>-5.648751898871367</v>
+        <v>-4.701843179364708</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.8114338671826</v>
       </c>
       <c r="E57">
-        <v>-9.948081321173721</v>
+        <v>-9.84235503851664</v>
       </c>
       <c r="F57">
-        <v>3.840323870054998</v>
+        <v>3.22953125852972</v>
       </c>
       <c r="G57">
-        <v>-5.161214478393979</v>
+        <v>-3.850655573580537</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.291990061229997</v>
       </c>
       <c r="E58">
-        <v>-8.130306569754762</v>
+        <v>-9.883573208934456</v>
       </c>
       <c r="F58">
-        <v>3.312812017799019</v>
+        <v>3.143293720316296</v>
       </c>
       <c r="G58">
-        <v>-5.012004880393487</v>
+        <v>-4.520243203807987</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.74010106314608</v>
       </c>
       <c r="E59">
-        <v>-8.877147031573765</v>
+        <v>-8.692312836476692</v>
       </c>
       <c r="F59">
-        <v>3.698677212978094</v>
+        <v>3.020463073220728</v>
       </c>
       <c r="G59">
-        <v>-6.160082210139499</v>
+        <v>-5.160088892910626</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.151460971747407</v>
       </c>
       <c r="E60">
-        <v>-8.676589974722061</v>
+        <v>-8.297158194567377</v>
       </c>
       <c r="F60">
-        <v>3.396499789488586</v>
+        <v>2.78686961810524</v>
       </c>
       <c r="G60">
-        <v>-6.202927290508747</v>
+        <v>-5.786881100951919</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.512174864662864</v>
       </c>
       <c r="E61">
-        <v>-8.11447049614994</v>
+        <v>-9.411991511197689</v>
       </c>
       <c r="F61">
-        <v>3.502592248763874</v>
+        <v>2.812934250061542</v>
       </c>
       <c r="G61">
-        <v>-6.963525128156302</v>
+        <v>-5.35089549561206</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.813092514679211</v>
       </c>
       <c r="E62">
-        <v>-7.824725143717167</v>
+        <v>-8.377977870182269</v>
       </c>
       <c r="F62">
-        <v>3.599530887847923</v>
+        <v>3.046842862654203</v>
       </c>
       <c r="G62">
-        <v>-7.031156262978073</v>
+        <v>-5.282929995690823</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.051712849232747</v>
       </c>
       <c r="E63">
-        <v>-8.56484082163478</v>
+        <v>-8.887603278057476</v>
       </c>
       <c r="F63">
-        <v>3.687543760392554</v>
+        <v>2.520485532010579</v>
       </c>
       <c r="G63">
-        <v>-7.090964578690546</v>
+        <v>-5.486929122366253</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.216268931419693</v>
       </c>
       <c r="E64">
-        <v>-8.204754682440862</v>
+        <v>-5.395284879608165</v>
       </c>
       <c r="F64">
-        <v>3.315939836982012</v>
+        <v>3.010699526252044</v>
       </c>
       <c r="G64">
-        <v>-7.238396413736449</v>
+        <v>-6.966200048952033</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.30720600350576</v>
       </c>
       <c r="E65">
-        <v>-7.512192510077797</v>
+        <v>-7.039410766728996</v>
       </c>
       <c r="F65">
-        <v>3.710097316334328</v>
+        <v>2.851636855223052</v>
       </c>
       <c r="G65">
-        <v>-7.545697803419297</v>
+        <v>-6.997441667206135</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.327486317733952</v>
       </c>
       <c r="E66">
-        <v>-7.747252010393942</v>
+        <v>-6.42001514890786</v>
       </c>
       <c r="F66">
-        <v>3.607043988710767</v>
+        <v>2.478906916906631</v>
       </c>
       <c r="G66">
-        <v>-7.309437410463669</v>
+        <v>-5.673614095871295</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.273915934213132</v>
       </c>
       <c r="E67">
-        <v>-7.347740976489248</v>
+        <v>-6.555864840663963</v>
       </c>
       <c r="F67">
-        <v>3.360313693026709</v>
+        <v>2.879484740040139</v>
       </c>
       <c r="G67">
-        <v>-7.025518403924694</v>
+        <v>-6.009078296456722</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.155687213448216</v>
       </c>
       <c r="E68">
-        <v>-7.267772653987797</v>
+        <v>-6.149710535390017</v>
       </c>
       <c r="F68">
-        <v>2.881027269601777</v>
+        <v>2.707668485274113</v>
       </c>
       <c r="G68">
-        <v>-7.803483363471265</v>
+        <v>-7.654965669488482</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.980019522184898</v>
       </c>
       <c r="E69">
-        <v>-7.911834869728714</v>
+        <v>-7.452701947039031</v>
       </c>
       <c r="F69">
-        <v>2.969333127740765</v>
+        <v>2.335362980143031</v>
       </c>
       <c r="G69">
-        <v>-8.418331123206867</v>
+        <v>-7.718081220194687</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.750453532291099</v>
       </c>
       <c r="E70">
-        <v>-6.542043937992553</v>
+        <v>-6.769128795581191</v>
       </c>
       <c r="F70">
-        <v>2.580254593259264</v>
+        <v>2.090023178252729</v>
       </c>
       <c r="G70">
-        <v>-8.339884436108298</v>
+        <v>-6.767136945675657</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.482011109017787</v>
       </c>
       <c r="E71">
-        <v>-7.420019950125674</v>
+        <v>-6.84851747340966</v>
       </c>
       <c r="F71">
-        <v>3.077669698298231</v>
+        <v>2.29616784244182</v>
       </c>
       <c r="G71">
-        <v>-8.39361127966513</v>
+        <v>-7.564650676631625</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.18144149949535</v>
       </c>
       <c r="E72">
-        <v>-7.276295242070232</v>
+        <v>-7.893843242496239</v>
       </c>
       <c r="F72">
-        <v>2.75382084306185</v>
+        <v>2.151122552470383</v>
       </c>
       <c r="G72">
-        <v>-8.658438370079129</v>
+        <v>-6.741702024297436</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.853871652896529</v>
       </c>
       <c r="E73">
-        <v>-7.891642404128511</v>
+        <v>-7.457126266144526</v>
       </c>
       <c r="F73">
-        <v>2.603411541154819</v>
+        <v>2.044140050470617</v>
       </c>
       <c r="G73">
-        <v>-8.356317984165241</v>
+        <v>-6.815338488727445</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.51511348171893</v>
       </c>
       <c r="E74">
-        <v>-7.483658595355466</v>
+        <v>-6.751725869969714</v>
       </c>
       <c r="F74">
-        <v>2.755884411869667</v>
+        <v>2.221928460243765</v>
       </c>
       <c r="G74">
-        <v>-8.677669329116755</v>
+        <v>-7.868876569508489</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.1669628725018</v>
       </c>
       <c r="E75">
-        <v>-7.067224654084107</v>
+        <v>-7.098955671455854</v>
       </c>
       <c r="F75">
-        <v>2.94597821660578</v>
+        <v>2.404710294768293</v>
       </c>
       <c r="G75">
-        <v>-7.787834414707131</v>
+        <v>-6.442127447903247</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.815954265678183</v>
       </c>
       <c r="E76">
-        <v>-7.215364624297028</v>
+        <v>-8.420364386894065</v>
       </c>
       <c r="F76">
-        <v>2.398394475577521</v>
+        <v>1.857227910918623</v>
       </c>
       <c r="G76">
-        <v>-7.229342071686543</v>
+        <v>-7.135627148560854</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.47117603390081</v>
       </c>
       <c r="E77">
-        <v>-8.904521656950132</v>
+        <v>-7.266717519544009</v>
       </c>
       <c r="F77">
-        <v>2.655410941182358</v>
+        <v>2.088311192158139</v>
       </c>
       <c r="G77">
-        <v>-8.201718818026816</v>
+        <v>-7.019566043045084</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.129956861331827</v>
       </c>
       <c r="E78">
-        <v>-9.214540987515246</v>
+        <v>-9.57008053880546</v>
       </c>
       <c r="F78">
-        <v>2.6932963540915</v>
+        <v>1.773644663819475</v>
       </c>
       <c r="G78">
-        <v>-7.767421590911985</v>
+        <v>-7.050228315829814</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.797592952894783</v>
       </c>
       <c r="E79">
-        <v>-9.329604983576141</v>
+        <v>-9.580088466362412</v>
       </c>
       <c r="F79">
-        <v>2.596934183960672</v>
+        <v>2.397760993211345</v>
       </c>
       <c r="G79">
-        <v>-7.693755331572122</v>
+        <v>-7.416560043023407</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.476159449103936</v>
       </c>
       <c r="E80">
-        <v>-9.708842039348495</v>
+        <v>-10.48159442943939</v>
       </c>
       <c r="F80">
-        <v>2.445189817966926</v>
+        <v>1.888894110697835</v>
       </c>
       <c r="G80">
-        <v>-6.961499074286268</v>
+        <v>-6.019936885825532</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.160849819317758</v>
       </c>
       <c r="E81">
-        <v>-12.12963291810285</v>
+        <v>-10.95140549383916</v>
       </c>
       <c r="F81">
-        <v>2.574648274318608</v>
+        <v>1.609099202911232</v>
       </c>
       <c r="G81">
-        <v>-6.638201128557662</v>
+        <v>-6.995799636618656</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.85693425771897</v>
       </c>
       <c r="E82">
-        <v>-11.13205537895314</v>
+        <v>-10.90853895888255</v>
       </c>
       <c r="F82">
-        <v>2.483734052536891</v>
+        <v>2.163092201779274</v>
       </c>
       <c r="G82">
-        <v>-6.443607261759301</v>
+        <v>-6.561317018953628</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.562066122377364</v>
       </c>
       <c r="E83">
-        <v>-12.80769944516736</v>
+        <v>-13.06510696471136</v>
       </c>
       <c r="F83">
-        <v>2.823117479097818</v>
+        <v>1.933283803801687</v>
       </c>
       <c r="G83">
-        <v>-6.011190424510777</v>
+        <v>-4.928642033169099</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.272345983084229</v>
       </c>
       <c r="E84">
-        <v>-13.79787745778853</v>
+        <v>-12.18204094779361</v>
       </c>
       <c r="F84">
-        <v>2.616703584903102</v>
+        <v>1.861294867709471</v>
       </c>
       <c r="G84">
-        <v>-5.88185403138253</v>
+        <v>-5.95962205664555</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.993188778239288</v>
       </c>
       <c r="E85">
-        <v>-14.6821978620064</v>
+        <v>-13.83778237074412</v>
       </c>
       <c r="F85">
-        <v>2.325569342761953</v>
+        <v>2.387948351359282</v>
       </c>
       <c r="G85">
-        <v>-5.800424542753077</v>
+        <v>-5.209399468718071</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.721432453955249</v>
       </c>
       <c r="E86">
-        <v>-16.19525612592322</v>
+        <v>-14.67418246301282</v>
       </c>
       <c r="F86">
-        <v>2.421998028541231</v>
+        <v>2.274041887097216</v>
       </c>
       <c r="G86">
-        <v>-5.379548267254452</v>
+        <v>-4.023734204919173</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.458272303951391</v>
       </c>
       <c r="E87">
-        <v>-17.71527918286385</v>
+        <v>-17.58059330892772</v>
       </c>
       <c r="F87">
-        <v>2.327718431689205</v>
+        <v>1.82936102163055</v>
       </c>
       <c r="G87">
-        <v>-5.271962158319218</v>
+        <v>-3.651112441200966</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.207786659039942</v>
       </c>
       <c r="E88">
-        <v>-18.27422420115659</v>
+        <v>-19.23836801670767</v>
       </c>
       <c r="F88">
-        <v>2.127077145556266</v>
+        <v>2.205277376248834</v>
       </c>
       <c r="G88">
-        <v>-4.038141699106082</v>
+        <v>-4.327261572687252</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-1.968257468610943</v>
       </c>
       <c r="E89">
-        <v>-20.79654799563692</v>
+        <v>-21.24259362844444</v>
       </c>
       <c r="F89">
-        <v>2.29415020110555</v>
+        <v>2.352321303085557</v>
       </c>
       <c r="G89">
-        <v>-4.685283830577274</v>
+        <v>-3.622943009207307</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.742757282101258</v>
       </c>
       <c r="E90">
-        <v>-21.91497692062932</v>
+        <v>-20.2377343030904</v>
       </c>
       <c r="F90">
-        <v>2.10916384794673</v>
+        <v>1.83330603306591</v>
       </c>
       <c r="G90">
-        <v>-4.279434121281401</v>
+        <v>-4.05990853602679</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.53222873977204</v>
       </c>
       <c r="E91">
-        <v>-23.21957594055106</v>
+        <v>-23.72784280622396</v>
       </c>
       <c r="F91">
-        <v>2.053683462317055</v>
+        <v>1.75600217992148</v>
       </c>
       <c r="G91">
-        <v>-4.192965982341177</v>
+        <v>-3.71940899567613</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.333192351672378</v>
       </c>
       <c r="E92">
-        <v>-24.76903860701555</v>
+        <v>-26.95769537966271</v>
       </c>
       <c r="F92">
-        <v>1.880611328760086</v>
+        <v>1.413844100596702</v>
       </c>
       <c r="G92">
-        <v>-3.824667791097258</v>
+        <v>-3.492209565861488</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.146440928973585</v>
       </c>
       <c r="E93">
-        <v>-26.80990863042239</v>
+        <v>-27.47118357586646</v>
       </c>
       <c r="F93">
-        <v>1.742922352765865</v>
+        <v>1.435227297866966</v>
       </c>
       <c r="G93">
-        <v>-3.331965919578606</v>
+        <v>-3.60612543786781</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-0.9685363270305867</v>
       </c>
       <c r="E94">
-        <v>-29.66126908206304</v>
+        <v>-29.73607041572174</v>
       </c>
       <c r="F94">
-        <v>1.323088249406529</v>
+        <v>1.705900059580637</v>
       </c>
       <c r="G94">
-        <v>-4.101038753806695</v>
+        <v>-3.309834922648577</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-0.7936885642341481</v>
       </c>
       <c r="E95">
-        <v>-32.15887646540951</v>
+        <v>-31.94172707979369</v>
       </c>
       <c r="F95">
-        <v>1.145223821749441</v>
+        <v>1.519054435677091</v>
       </c>
       <c r="G95">
-        <v>-3.135117571268002</v>
+        <v>-2.94933968724072</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.6189705951893174</v>
       </c>
       <c r="E96">
-        <v>-33.47673032875169</v>
+        <v>-33.70105508143266</v>
       </c>
       <c r="F96">
-        <v>0.9214540944274238</v>
+        <v>1.400236899371247</v>
       </c>
       <c r="G96">
-        <v>-3.785931097742246</v>
+        <v>-2.678030548660829</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-0.4400532460412138</v>
       </c>
       <c r="E97">
-        <v>-36.26354191188701</v>
+        <v>-35.2199663980044</v>
       </c>
       <c r="F97">
-        <v>0.6147235164310271</v>
+        <v>1.121084976186312</v>
       </c>
       <c r="G97">
-        <v>-3.572950461018773</v>
+        <v>-3.622390148102249</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-0.2503126538551679</v>
       </c>
       <c r="E98">
-        <v>-38.4103012430152</v>
+        <v>-36.7555040068953</v>
       </c>
       <c r="F98">
-        <v>0.8567993004296084</v>
+        <v>0.7596215217523284</v>
       </c>
       <c r="G98">
-        <v>-4.021724703776836</v>
+        <v>-3.428508048594832</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-0.05158011457642431</v>
       </c>
       <c r="E99">
-        <v>-39.09462385692132</v>
+        <v>-40.44086672381759</v>
       </c>
       <c r="F99">
-        <v>0.5700978511457743</v>
+        <v>0.2402633794019892</v>
       </c>
       <c r="G99">
-        <v>-3.200997427499498</v>
+        <v>-3.968183250770203</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>0.1630539955640398</v>
       </c>
       <c r="E100">
-        <v>-43.092532792905</v>
+        <v>-42.48741545363005</v>
       </c>
       <c r="F100">
-        <v>0.5402909221112885</v>
+        <v>0.08165919123551714</v>
       </c>
       <c r="G100">
-        <v>-3.386434325336234</v>
+        <v>-3.151988111336128</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>0.3835595317233438</v>
       </c>
       <c r="E101">
-        <v>-45.41206925708484</v>
+        <v>-45.99863796682438</v>
       </c>
       <c r="F101">
-        <v>-0.04677223183000257</v>
+        <v>-0.01834787805969537</v>
       </c>
       <c r="G101">
-        <v>-3.620609074602121</v>
+        <v>-3.251513041883237</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>0.61902977469589</v>
       </c>
       <c r="E102">
-        <v>-47.07520794232688</v>
+        <v>-48.31170324164727</v>
       </c>
       <c r="F102">
-        <v>-0.3182819821199837</v>
+        <v>-0.30422263285567</v>
       </c>
       <c r="G102">
-        <v>-4.647815076163803</v>
+        <v>-4.788847626682295</v>
       </c>
     </row>
   </sheetData>
